--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:49:07+00:00</t>
+    <t>2026-09-24T09:21:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T09:21:38+00:00</t>
+    <t>2026-09-25T09:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T09:25:52+00:00</t>
+    <t>2026-09-29T08:39:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:39:07+00:00</t>
+    <t>2026-09-29T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T12:08:37+00:00</t>
+    <t>2026-09-29T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T14:44:05+00:00</t>
+    <t>2026-09-30T08:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:52:41+00:00</t>
+    <t>2026-10-01T10:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T10:22:30+00:00</t>
+    <t>2026-10-01T13:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:25:50+00:00</t>
+    <t>2026-10-02T10:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:10:21+00:00</t>
+    <t>2026-10-05T15:45:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T15:45:17+00:00</t>
+    <t>2026-10-06T07:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:55:41+00:00</t>
+    <t>2026-10-12T15:02:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:02:09+00:00</t>
+    <t>2026-10-16T07:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:19:18+00:00</t>
+    <t>2026-10-16T09:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:33:06+00:00</t>
+    <t>2026-10-19T09:41:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T09:41:59+00:00</t>
+    <t>2026-10-19T12:39:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:39:20+00:00</t>
+    <t>2026-10-20T08:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:00:54+00:00</t>
+    <t>2026-10-20T09:17:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T09:17:11+00:00</t>
+    <t>2026-10-20T10:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T10:27:48+00:00</t>
+    <t>2026-10-22T10:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T10:11:54+00:00</t>
+    <t>2026-10-23T10:00:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T10:00:11+00:00</t>
+    <t>2026-10-26T09:53:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T09:53:40+00:00</t>
+    <t>2026-10-26T13:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:08:53+00:00</t>
+    <t>2026-10-26T14:17:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T14:17:26+00:00</t>
+    <t>2026-10-28T14:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:42:40+00:00</t>
+    <t>2026-10-29T08:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:18:15+00:00</t>
+    <t>2026-10-29T10:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:09:40+00:00</t>
+    <t>2026-10-30T10:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
